--- a/stories/arbres/ATOM-REL.AMI.001-02.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est dans la cour. Papa attend près du portail. Hugo a un cerceau bleu. Lina est là aussi. Hugo veut jouer. Papa dit : tu peux inviter. Inviter, c'est demander. Hugo dit : tu veux jouer ? Lina secoue la tête. Lina dit : non. Hugo a le ventre un peu serré. Papa s'approche. Papa dit : on peut accepter un non. Accepter un non, c'est possible. Hugo dit : d'accord. Il joue avec papa. Le cerceau roule sur l'asphalte. Lina joue au bac à sable. Hugo n'insiste pas. Parce qu'il accepte un non, le jeu reste doux. Papa dit : merci. Tu as su inviter. Tu as su accepter un non. Hugo sourit un peu.</t>
+          <t>Hugo est dans la cour. Papa attend près du portail. Hugo a un cerceau bleu. Lina est là aussi. Hugo veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Lina secoue la tête. Non. Hugo a le ventre un peu serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Il joue avec papa. Le cerceau roule sur l'asphalte. Lina joue au bac à sable. Hugo n'insiste pas. Parce qu'il accepte un non, le jeu reste doux. Merci. Tu as su inviter. Tu as su accepter un non. Hugo sourit un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,21 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est dans la cour. Papa attend près du portail. Hugo a un cerceau bleu. Lina est là aussi. Hugo veut jouer.
+papa|Tu peux inviter. Inviter, c'est demander.
+enfant-m|Tu veux jouer ?
+narrateur|Lina secoue la tête.
+copine|Non.
+narrateur|Hugo a le ventre un peu serré. Papa s'approche.
+papa|On peut accepter un non. Accepter un non, c'est possible.
+enfant-m|D'accord. Il joue avec papa.
+narrateur|Le cerceau roule sur l'asphalte. Lina joue au bac à sable. Hugo n'insiste pas. Parce qu'il accepte un non, le jeu reste doux.
+papa|Merci. Tu as su inviter. Tu as su accepter un non.
+narrateur|Hugo sourit un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Lina dit non. Que fait Hugo ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a su inviter. Lina a dit non. Hugo a pu accepter un non. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo range le cerceau. Papa ouvre le portail.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-02.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1320,6 +1325,11 @@
 narrateur|Hugo sourit un peu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1513,7 @@
           <t>narrateur|Lina dit non. Que fait Hugo ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1685,7 @@
           <t>narrateur|Hugo a su inviter. Lina a dit non. Hugo a pu accepter un non. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1849,7 @@
           <t>narrateur|Hugo range le cerceau. Papa ouvre le portail.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.AMI.001-02.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hugo invite Lina</t>
+          <t>Le cerceau d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un cerceau bleu attend contre la grille. Amir invite Mila. Elle dit non. Il joue avec papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est dans la cour. Papa attend près du portail. Hugo a un cerceau bleu. Lina est là aussi. Hugo veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Lina secoue la tête. Non. Hugo a le ventre un peu serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Il joue avec papa. Le cerceau roule sur l'asphalte. Lina joue au bac à sable. Hugo n'insiste pas. Parce qu'il accepte un non, le jeu reste doux. Merci. Tu as su inviter. Tu as su accepter un non. Hugo sourit un peu.</t>
+          <t>Un cerceau bleu attend contre la grille. De la craie blanche est sur l'asphalte. La cloche a laissé un petit écho. Le portail sent le fer chaud. Papa attend près du portail. Une feuille sèche tourne au vent. Amir, ton cerceau est là. En ce moment, Amir prend le cerceau. Le plastique est lisse et un peu chaud. Il est bleu, papa. Oui. Mila est là aussi. Mila a un seau de sable. Amir veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Non. Mila secoue la tête. Amir a le ventre un peu serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Il joue avec papa. Le cerceau roule sur l'asphalte. Mila joue au bac à sable. Le sable est chaud. Amir continue son jeu. Merci. Tu as su inviter. Tu as su accepter un non. Amir sourit un peu. Tu as fait du bon travail. Le jeu reste doux. Le cerceau roule loin. Oui. Amir pousse encore le cerceau. Il s'arrête près d'un trait de craie. La craie est blanche. Oui. Tu as invité. Mila a dit non. Tu as accepté un non. D'accord. Le sable du bac sent le soleil. Mila verse encore un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1324,53 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugo est dans la cour. Papa attend près du portail. Hugo a un cerceau bleu. Lina est là aussi. Hugo veut jouer.
-papa|Tu peux inviter. Inviter, c'est demander.
+          <t>narrateur|Un cerceau bleu attend contre la grille.
+narrateur|De la craie blanche est sur l'asphalte.
+narrateur|La cloche a laissé un petit écho.
+narrateur|Le portail sent le fer chaud.
+narrateur|Papa attend près du portail.
+narrateur|Une feuille sèche tourne au vent.
+papa|Amir, ton cerceau est là.
+narrateur|En ce moment, Amir prend le cerceau.
+narrateur|Le plastique est lisse et un peu chaud.
+enfant-m|Il est bleu, papa.
+papa|Oui.
+narrateur|Mila est là aussi.
+narrateur|Mila a un seau de sable.
+narrateur|Amir veut jouer.
+papa|Tu peux inviter.
+papa|Inviter, c'est demander.
 enfant-m|Tu veux jouer ?
-narrateur|Lina secoue la tête.
 copine|Non.
-narrateur|Hugo a le ventre un peu serré. Papa s'approche.
-papa|On peut accepter un non. Accepter un non, c'est possible.
-enfant-m|D'accord. Il joue avec papa.
-narrateur|Le cerceau roule sur l'asphalte. Lina joue au bac à sable. Hugo n'insiste pas. Parce qu'il accepte un non, le jeu reste doux.
-papa|Merci. Tu as su inviter. Tu as su accepter un non.
-narrateur|Hugo sourit un peu.</t>
+narrateur|Mila secoue la tête.
+narrateur|Amir a le ventre un peu serré.
+narrateur|Papa s'approche.
+papa|On peut accepter un non.
+papa|Accepter un non, c'est possible.
+enfant-m|D'accord.
+narrateur|Il joue avec papa.
+narrateur|Le cerceau roule sur l'asphalte.
+narrateur|Mila joue au bac à sable.
+narrateur|Le sable est chaud.
+narrateur|Amir continue son jeu.
+papa|Merci.
+papa|Tu as su inviter.
+papa|Tu as su accepter un non.
+narrateur|Amir sourit un peu.
+papa|Tu as fait du bon travail.
+papa|Le jeu reste doux.
+enfant-m|Le cerceau roule loin.
+papa|Oui.
+narrateur|Amir pousse encore le cerceau.
+narrateur|Il s'arrête près d'un trait de craie.
+enfant-m|La craie est blanche.
+papa|Oui.
+papa|Tu as invité.
+papa|Mila a dit non.
+papa|Tu as accepté un non.
+enfant-m|D'accord.
+narrateur|Le sable du bac sent le soleil.
+narrateur|Mila verse encore un peu.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1354,7 +1402,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lina dit non. Que fait Hugo ?</t>
+          <t>Mila dit non. Que fait Amir ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1510,7 +1558,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Lina dit non. Que fait Hugo ?</t>
+          <t>narrateur|Mila dit non.
+narrateur|Que fait Amir ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1538,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo a su inviter. Lina a dit non. Hugo a pu accepter un non. Papa est là.</t>
+          <t>Amir a su inviter. Mila a dit non. Amir a pu accepter un non. Je suis près de toi. Tu as accepté un non ? Oui, papa. Bravo. Tu as fait du bon travail. Le cerceau s'arrête près d'une craie. Mila verse le sable. Amir reprend le cerceau. À toi, papa. Merci. On peut inviter. On peut accepter un non. Le portail reste un peu chaud. Il sent le fer. Oui. Tu as demandé. Tu as accepté un non. Oui, papa. Une feuille sèche tourne encore. Amir attend son tour avec papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1682,7 +1731,29 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a su inviter. Lina a dit non. Hugo a pu accepter un non. Papa est là.</t>
+          <t>narrateur|Amir a su inviter.
+narrateur|Mila a dit non.
+narrateur|Amir a pu accepter un non.
+papa|Je suis près de toi.
+papa|Tu as accepté un non ?
+enfant-m|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le cerceau s'arrête près d'une craie.
+narrateur|Mila verse le sable.
+narrateur|Amir reprend le cerceau.
+enfant-m|À toi, papa.
+papa|Merci.
+papa|On peut inviter.
+papa|On peut accepter un non.
+narrateur|Le portail reste un peu chaud.
+enfant-m|Il sent le fer.
+papa|Oui.
+papa|Tu as demandé.
+papa|Tu as accepté un non.
+enfant-m|Oui, papa.
+narrateur|Une feuille sèche tourne encore.
+narrateur|Amir attend son tour avec papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1710,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hugo range le cerceau. Papa ouvre le portail.</t>
+          <t>On range le cerceau ? Oui. Amir range le cerceau. Papa ouvre le portail. La feuille sèche s'envole. Tu as fini de jouer ? Oui, papa. Merci. Bravo. Mila agite la main. Au revoir. Au revoir. L'asphalte redevient calme. Tu as su inviter, Amir. Oui. Le cerceau bleu tapote la grille. La cour sent encore le soleil.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1917,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hugo range le cerceau. Papa ouvre le portail.</t>
+          <t>papa|On range le cerceau ?
+enfant-m|Oui.
+narrateur|Amir range le cerceau.
+narrateur|Papa ouvre le portail.
+narrateur|La feuille sèche s'envole.
+papa|Tu as fini de jouer ?
+enfant-m|Oui, papa.
+papa|Merci.
+papa|Bravo.
+narrateur|Mila agite la main.
+copine|Au revoir.
+enfant-m|Au revoir.
+narrateur|L'asphalte redevient calme.
+papa|Tu as su inviter, Amir.
+enfant-m|Oui.
+narrateur|Le cerceau bleu tapote la grille.
+narrateur|La cour sent encore le soleil.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1874,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai invité. Mila a dit non. Tu as accepté un non. Bravo, Amir. Le cerceau bleu attend contre la grille. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,7 +2101,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai invité.
+enfant-m|Mila a dit non.
+papa|Tu as accepté un non.
+papa|Bravo, Amir.
+narrateur|Le cerceau bleu attend contre la grille.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2036,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2166,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-02.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un cerceau bleu attend contre la grille. De la craie blanche est sur l'asphalte. La cloche a laissé un petit écho. Le portail sent le fer chaud. Papa attend près du portail. Une feuille sèche tourne au vent. Amir, ton cerceau est là. En ce moment, Amir prend le cerceau. Le plastique est lisse et un peu chaud. Il est bleu, papa. Oui. Mila est là aussi. Mila a un seau de sable. Amir veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Non. Mila secoue la tête. Amir a le ventre un peu serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Il joue avec papa. Le cerceau roule sur l'asphalte. Mila joue au bac à sable. Le sable est chaud. Amir continue son jeu. Merci. Tu as su inviter. Tu as su accepter un non. Amir sourit un peu. Tu as fait du bon travail. Le jeu reste doux. Le cerceau roule loin. Oui. Amir pousse encore le cerceau. Il s'arrête près d'un trait de craie. La craie est blanche. Oui. Tu as invité. Mila a dit non. Tu as accepté un non. D'accord. Le sable du bac sent le soleil. Mila verse encore un peu.</t>
+          <t>Un cerceau bleu attend contre la grille. De la craie blanche est sur l'asphalte. La cloche a laissé un petit écho. Le portail sent le fer chaud. Papa attend près du portail. Une feuille sèche tourne au vent. Amir, ton cerceau est là. En ce moment, Amir prend le cerceau. Le plastique est lisse et un peu chaud. Il est bleu, papa. Oui. Mila est là aussi. Mila a un seau de sable. Amir veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Non. Mila secoue la tête. Amir a le ventre un peu serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Il joue avec papa. Le cerceau roule sur l'asphalte. Mila joue au bac à sable. Le sable est chaud. Amir continue son jeu. Merci. Tu as su inviter. Tu as su accepter un non. Amir sourit un peu. Le jeu reste doux. Le cerceau roule loin. Oui. Amir pousse encore le cerceau. Il s'arrête près d'un trait de craie. La craie est blanche. Oui. Tu as invité. Mila a dit non. Tu as accepté un non. D'accord. Le sable du bac sent le soleil. Mila verse encore un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo est dans la cour. Papa attend près du portail. Hugo a un cerceau bleu. Lina est là aussi. Hugo veut jouer. Papa dit : tu peux &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Inviter, c'est demander. Hugo dit : tu veux jouer ? Lina secoue la tête. Lina dit : non. Hugo a le ventre un peu serré. Papa s'approche. Papa dit : on peut accepter un non. Accepter un non, c'est possible. Hugo dit : d'accord. Il joue avec papa. Le cerceau roule sur l'asphalte. Lina joue au bac à sable. Hugo n'insiste pas. Parce qu'il accepte un non, le jeu reste doux. Papa dit : merci. Tu as su inviter. Tu as su accepter un non. Hugo sourit un peu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un cerceau bleu attend contre la grille. De la craie blanche est sur l'asphalte. La cloche a laissé un petit écho. Le portail sent le fer chaud. Papa attend près du portail. Une feuille sèche tourne au vent. Amir, ton cerceau est là. En ce moment, Amir prend le cerceau. Le plastique est lisse et un peu chaud. Il est bleu, papa. Oui. Mila est là aussi. Mila a un seau de sable. Amir veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Non. Mila secoue la tête. Amir a le ventre un peu serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Il joue avec papa. Le cerceau roule sur l'asphalte. Mila joue au bac à sable. Le sable est chaud. Amir continue son jeu. Merci. Tu as su inviter. Tu as su accepter un non. Amir sourit un peu. Le jeu reste doux. Le cerceau roule loin. Oui. Amir pousse encore le cerceau. Il s'arrête près d'un trait de craie. La craie est blanche. Oui. Tu as invité. Mila a dit non. Tu as accepté un non. D'accord. Le sable du bac sent le soleil. Mila verse encore un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1357,7 +1357,6 @@
 papa|Tu as su inviter.
 papa|Tu as su accepter un non.
 narrateur|Amir sourit un peu.
-papa|Tu as fait du bon travail.
 papa|Le jeu reste doux.
 enfant-m|Le cerceau roule loin.
 papa|Oui.
@@ -1407,7 +1406,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Lina dit non. Que fait Hugo ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila dit non. Que fait Amir ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1562,7 +1561,6 @@
 narrateur|Que fait Amir ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1587,12 +1585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a su inviter. Mila a dit non. Amir a pu accepter un non. Je suis près de toi. Tu as accepté un non ? Oui, papa. Bravo. Tu as fait du bon travail. Le cerceau s'arrête près d'une craie. Mila verse le sable. Amir reprend le cerceau. À toi, papa. Merci. On peut inviter. On peut accepter un non. Le portail reste un peu chaud. Il sent le fer. Oui. Tu as demandé. Tu as accepté un non. Oui, papa. Une feuille sèche tourne encore. Amir attend son tour avec papa.</t>
+          <t>Amir a su inviter. Mila a dit non. Amir a pu accepter un non. Je suis près de toi. Tu as accepté un non ? Oui, papa. Bravo. Le cerceau s'arrête près d'une craie. Mila verse le sable. Amir reprend le cerceau. À toi, papa. Merci. On peut inviter. On peut accepter un non. Le portail reste un peu chaud. Il sent le fer. Oui. Tu as demandé. Tu as accepté un non. Oui, papa. Une feuille sèche tourne encore. Amir attend son tour avec papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo a su &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Lina a dit non. Hugo a pu accepter un non. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a su inviter. Mila a dit non. Amir a pu accepter un non. Je suis près de toi. Tu as accepté un non ? Oui, papa. Bravo. Le cerceau s'arrête près d'une craie. Mila verse le sable. Amir reprend le cerceau. À toi, papa. Merci. On peut inviter. On peut accepter un non. Le portail reste un peu chaud. Il sent le fer. Oui. Tu as demandé. Tu as accepté un non. Oui, papa. Une feuille sèche tourne encore. Amir attend son tour avec papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1738,7 +1736,6 @@
 papa|Tu as accepté un non ?
 enfant-m|Oui, papa.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Le cerceau s'arrête près d'une craie.
 narrateur|Mila verse le sable.
 narrateur|Amir reprend le cerceau.
@@ -1756,7 +1753,6 @@
 narrateur|Amir attend son tour avec papa.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1786,7 +1782,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo range le cerceau. Papa ouvre le portail.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range le cerceau ? Oui. Amir range le cerceau. Papa ouvre le portail. La feuille sèche s'envole. Tu as fini de jouer ? Oui, papa. Merci. Bravo. Mila agite la main. Au revoir. Au revoir. L'asphalte redevient calme. Tu as su inviter, Amir. Oui. Le cerceau bleu tapote la grille. La cour sent encore le soleil.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1936,7 +1932,6 @@
 narrateur|La cour sent encore le soleil.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai invité. Mila a dit non. Tu as accepté un non. Bravo, Amir. Le cerceau bleu attend contre la grille. L'histoire est finie.</t>
+          <t>J'ai invité. Mila a dit non. Tu as accepté un non. Bravo, Amir. Le cerceau bleu attend contre la grille.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai invité. Mila a dit non. Tu as accepté un non. Bravo, Amir. Le cerceau bleu attend contre la grille.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2105,11 +2100,9 @@
 enfant-m|Mila a dit non.
 papa|Tu as accepté un non.
 papa|Bravo, Amir.
-narrateur|Le cerceau bleu attend contre la grille.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le cerceau bleu attend contre la grille.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2128,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2173,6 +2166,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-02.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hugo, Lina, papa</t>
+          <t>Amir, Mila, papa</t>
         </is>
       </c>
     </row>
